--- a/Assets/Resources/VNovelizerRes/ExcelVNScripts/sntzm_clark4F(3).xlsx
+++ b/Assets/Resources/VNovelizerRes/ExcelVNScripts/sntzm_clark4F(3).xlsx
@@ -603,11 +603,16 @@
         <rFont val="Calibri"/>
         <charset val="134"/>
       </rPr>
-      <t>_1, 1)</t>
+      <t>_3, 3)</t>
     </r>
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>源类型</t>
     </r>
     <r>
@@ -967,6 +972,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
       <t>charfadeout(L,1)&amp;loadScript(</t>
     </r>
     <r>
@@ -5896,7 +5906,6 @@
       <c r="J83" t="s">
         <v>15</v>
       </c>
-      <c r="K83"/>
       <c r="L83" t="s">
         <v>89</v>
       </c>

--- a/Assets/Resources/VNovelizerRes/ExcelVNScripts/sntzm_clark4F(3).xlsx
+++ b/Assets/Resources/VNovelizerRes/ExcelVNScripts/sntzm_clark4F(3).xlsx
@@ -579,7 +579,7 @@
         <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
-      <t>克拉克线</t>
+      <t>sntzm_clark4F(4)</t>
     </r>
     <r>
       <rPr>
@@ -587,23 +587,7 @@
         <rFont val="Calibri"/>
         <charset val="134"/>
       </rPr>
-      <t>4</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>层（终）</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t>_3, 3)</t>
+      <t>, 3)</t>
     </r>
   </si>
   <si>
